--- a/Data/mcdonald_2016_supinfo.xlsx
+++ b/Data/mcdonald_2016_supinfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/wadh6549_ox_ac_uk/Documents/UNI/Masters/Project resources/Badger-MBIOL/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_F25DC773A252ABDACC104897F11C74365ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BBE5F2F-261B-417D-B11D-26CA463B5763}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="11_F25DC773A252ABDACC104897F11C74365ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C8E7F5B-5D75-4467-9780-C394D3F62194}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
     <t>(0.86,1.31)</t>
   </si>
@@ -101,136 +101,67 @@
     <t>(0.78,1.13)</t>
   </si>
   <si>
-    <t>Ntot[1]</t>
-  </si>
-  <si>
     <t>(61.08,90.81)</t>
   </si>
   <si>
-    <t>Ntot[2]</t>
-  </si>
-  <si>
     <t>(67.01,93.43)</t>
   </si>
   <si>
-    <t>Ntot[3]</t>
-  </si>
-  <si>
     <t>(96.67,129.85)</t>
   </si>
   <si>
-    <t>Ntot[4]</t>
-  </si>
-  <si>
     <t>(100.02,129.05)</t>
   </si>
   <si>
-    <t>Ntot[5]</t>
-  </si>
-  <si>
     <t>(116.7,151.21)</t>
   </si>
   <si>
-    <t>Ntot[6]</t>
-  </si>
-  <si>
     <t>(127.8,160.2)</t>
   </si>
   <si>
-    <t>Ntot[7]</t>
-  </si>
-  <si>
     <t>(117.9,148.25)</t>
   </si>
   <si>
-    <t>Ntot[8]</t>
-  </si>
-  <si>
     <t>(127.4,161.3)</t>
   </si>
   <si>
-    <t>Ntot[9]</t>
-  </si>
-  <si>
     <t>(137.5,172.11)</t>
   </si>
   <si>
-    <t>Ntot[10]</t>
-  </si>
-  <si>
     <t>(146.2,180.85)</t>
   </si>
   <si>
-    <t>Ntot[11]</t>
-  </si>
-  <si>
     <t>(149.6,185.7)</t>
   </si>
   <si>
-    <t>Ntot[12]</t>
-  </si>
-  <si>
     <t>(139.85,173.8)</t>
   </si>
   <si>
-    <t>Ntot[13]</t>
-  </si>
-  <si>
     <t>(134.65,168.4)</t>
   </si>
   <si>
-    <t>Ntot[14]</t>
-  </si>
-  <si>
     <t>(100.1,133.5)</t>
   </si>
   <si>
-    <t>Ntot[15]</t>
-  </si>
-  <si>
     <t>(132.9,167.4)</t>
   </si>
   <si>
-    <t>Ntot[16]</t>
-  </si>
-  <si>
     <t>(151.1,189.31)</t>
   </si>
   <si>
-    <t>Ntot[17]</t>
-  </si>
-  <si>
-    <t>Ntot[18]</t>
-  </si>
-  <si>
     <t>(114.25,146.56)</t>
   </si>
   <si>
-    <t>Ntot[19]</t>
-  </si>
-  <si>
     <t>(96.61,128.5)</t>
   </si>
   <si>
-    <t>Ntot[20]</t>
-  </si>
-  <si>
     <t>(79.59,105.2)</t>
   </si>
   <si>
-    <t>Ntot[21]</t>
-  </si>
-  <si>
     <t>(76.26,103.4)</t>
   </si>
   <si>
-    <t>Ntot[22]</t>
-  </si>
-  <si>
     <t>(68.79,93.32)</t>
-  </si>
-  <si>
-    <t>Ntot[23]</t>
   </si>
   <si>
     <t>(62.97,90.17)</t>
@@ -278,7 +209,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -294,19 +225,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -336,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -344,13 +262,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -368,6 +283,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -633,30 +552,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1984</v>
       </c>
@@ -666,475 +585,406 @@
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="2">
+        <v>75.55</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="3">
-        <v>75.55</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1985</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>1.42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="D3" s="2">
         <v>79.89</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <f>A3+1</f>
         <v>1986</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>1.01</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="D4" s="2">
         <v>113.06</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <f t="shared" ref="A5:A24" si="0">A4+1</f>
         <v>1987</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>1.17</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="2">
+        <v>114.24</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>1988</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1.08</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2">
+        <v>133.25</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>1989</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.93</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2">
+        <v>143.5</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>1990</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1.08</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2">
+        <v>132.65</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="3">
-        <v>114.24</v>
-      </c>
-      <c r="F5" s="3" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>1991</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1.08</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2">
+        <v>143.44</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <f t="shared" si="0"/>
-        <v>1988</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1.08</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="s">
+    <row r="10" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>1992</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1.06</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2">
+        <v>154.41</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="3">
-        <v>133.25</v>
-      </c>
-      <c r="F6" s="3" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>1993</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1.03</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2">
+        <v>163.43</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <f t="shared" si="0"/>
-        <v>1989</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0.93</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2" t="s">
+    <row r="12" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>1994</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2">
+        <v>167.22</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="3">
-        <v>143.5</v>
-      </c>
-      <c r="F7" s="3" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>1995</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2">
+        <v>156.11000000000001</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <f t="shared" si="0"/>
-        <v>1990</v>
-      </c>
-      <c r="B8" s="3">
-        <v>1.08</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="2" t="s">
+    <row r="14" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>1996</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.77</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="2">
+        <v>151.16999999999999</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="3">
-        <v>132.65</v>
-      </c>
-      <c r="F8" s="3" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>1997</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="2">
+        <v>115.78</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <f t="shared" si="0"/>
-        <v>1991</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1.08</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2" t="s">
+    <row r="16" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>1998</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2">
+        <v>149.87</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="3">
-        <v>143.44</v>
-      </c>
-      <c r="F9" s="3" t="s">
+    </row>
+    <row r="17" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>1999</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.84</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="2">
+        <v>169.58</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <f t="shared" si="0"/>
-        <v>1992</v>
-      </c>
-      <c r="B10" s="3">
-        <v>1.06</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="2" t="s">
+    <row r="18" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="2">
+        <v>142.61000000000001</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-126160.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>2001</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.87</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="2">
+        <v>129.66</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="3">
-        <v>154.41</v>
-      </c>
-      <c r="F10" s="3" t="s">
+    </row>
+    <row r="20" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>2002</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.82</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="2">
+        <v>112.25</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <f t="shared" si="0"/>
-        <v>1993</v>
-      </c>
-      <c r="B11" s="3">
-        <v>1.03</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
+    <row r="21" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>2003</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="2">
+        <v>91.65</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="3">
-        <v>163.43</v>
-      </c>
-      <c r="F11" s="3" t="s">
+    </row>
+    <row r="22" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>2004</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="2">
+        <v>89.41</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <f t="shared" si="0"/>
-        <v>1994</v>
-      </c>
-      <c r="B12" s="3">
-        <v>0.94</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
+    <row r="23" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>2005</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="2">
+        <v>80.12</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="3">
-        <v>167.22</v>
-      </c>
-      <c r="F12" s="3" t="s">
+    </row>
+    <row r="24" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>2006</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="2">
+        <v>75.819999999999993</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <f t="shared" si="0"/>
-        <v>1995</v>
-      </c>
-      <c r="B13" s="3">
-        <v>0.97</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="3">
-        <v>156.11000000000001</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <f t="shared" si="0"/>
-        <v>1996</v>
-      </c>
-      <c r="B14" s="3">
-        <v>0.77</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="3">
-        <v>151.16999999999999</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <f t="shared" si="0"/>
-        <v>1997</v>
-      </c>
-      <c r="B15" s="3">
-        <v>1.3</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="3">
-        <v>115.78</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <f t="shared" si="0"/>
-        <v>1998</v>
-      </c>
-      <c r="B16" s="3">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="3">
-        <v>149.87</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <f t="shared" si="0"/>
-        <v>1999</v>
-      </c>
-      <c r="B17" s="3">
-        <v>0.84</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="3">
-        <v>169.58</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <f t="shared" si="0"/>
-        <v>2000</v>
-      </c>
-      <c r="B18" s="3">
-        <v>0.91</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="3">
-        <v>142.61000000000001</v>
-      </c>
-      <c r="F18" s="4">
-        <v>-126160.1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <f t="shared" si="0"/>
-        <v>2001</v>
-      </c>
-      <c r="B19" s="3">
-        <v>0.87</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="3">
-        <v>129.66</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <f t="shared" si="0"/>
-        <v>2002</v>
-      </c>
-      <c r="B20" s="3">
-        <v>0.82</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="3">
-        <v>112.25</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <f t="shared" si="0"/>
-        <v>2003</v>
-      </c>
-      <c r="B21" s="3">
-        <v>0.98</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="3">
-        <v>91.65</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <f t="shared" si="0"/>
-        <v>2004</v>
-      </c>
-      <c r="B22" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" s="3">
-        <v>89.41</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <f t="shared" si="0"/>
-        <v>2005</v>
-      </c>
-      <c r="B23" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="3">
-        <v>80.12</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <f t="shared" si="0"/>
-        <v>2006</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" s="3">
-        <v>75.819999999999993</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
